--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_THE FITZGERALD EL PILAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_THE FITZGERALD EL PILAR.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7009</v>
+        <v>4.8635</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1366</v>
+        <v>0.3727</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8375</v>
+        <v>4.4908</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2557</v>
+        <v>-0.2424</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1909</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4467</v>
+        <v>-1.4524</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.0231</v>
+        <v>-1.7953</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2069</v>
+        <v>1.3651</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.23</v>
+        <v>-3.1604</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7674</v>
+        <v>1.5529</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0159</v>
+        <v>-0.1551</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7834</v>
+        <v>1.708</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8186</v>
+        <v>0.7853</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6293</v>
+        <v>0.6516</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1893</v>
+        <v>0.1337</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9388</v>
+        <v>7.0469</v>
       </c>
       <c r="W2" t="n">
-        <v>6.2587</v>
+        <v>6.3848</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5202</v>
+        <v>2.4907</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1525</v>
+        <v>2.2551</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3677</v>
+        <v>0.2356</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6826</v>
+        <v>2.6682</v>
       </c>
       <c r="H3" t="n">
-        <v>0.911</v>
+        <v>0.9226</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7716</v>
+        <v>1.7456</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2413</v>
+        <v>2.3234</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5614</v>
+        <v>1.6344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4413</v>
+        <v>0.3448</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0917</v>
+        <v>1.0566</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7028</v>
+        <v>-0.677</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0888</v>
+        <v>-0.0683</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.614</v>
+        <v>-0.6088</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7864</v>
+        <v>1.8744</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4443</v>
+        <v>-0.0659</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2307</v>
+        <v>1.9403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2592</v>
+        <v>0.3239</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6952</v>
+        <v>1.734</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.436</v>
+        <v>-1.4101</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2233</v>
+        <v>-0.9816</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1248</v>
+        <v>2.276</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.3481</v>
+        <v>-3.2576</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4825</v>
+        <v>1.3055</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4297</v>
+        <v>-0.542</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9121</v>
+        <v>1.8475</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4725</v>
+        <v>-0.4758</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.54</v>
+        <v>-0.5011</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0675</v>
+        <v>0.0253</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3791</v>
+        <v>1.2668</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1359</v>
+        <v>-0.0775</v>
       </c>
       <c r="F6" t="n">
-        <v>1.515</v>
+        <v>1.3443</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9941</v>
+        <v>0.9409</v>
       </c>
       <c r="H6" t="n">
-        <v>1.436</v>
+        <v>1.4111</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4418</v>
+        <v>-0.4702</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7598</v>
+        <v>0.7789</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6798</v>
+        <v>0.6979</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2343</v>
+        <v>0.1619</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7562</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.916</v>
+        <v>-0.8872</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1046</v>
+        <v>0.1172</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0206</v>
+        <v>-1.0044</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5007</v>
+        <v>0.4342</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5007</v>
+        <v>0.4342</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7473</v>
+        <v>0.6384</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.85</v>
+        <v>-0.7333</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5973</v>
+        <v>1.3717</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5425</v>
+        <v>0.5253</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8761</v>
+        <v>0.8364</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3337</v>
+        <v>-0.3111</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6342</v>
+        <v>-0.5735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7542</v>
+        <v>-0.6967</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1767</v>
+        <v>1.0988</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7562</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0643</v>
+        <v>1.0294</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5344</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5395</v>
+        <v>0.495</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3755</v>
+        <v>0.4537</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9387</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3142</v>
+        <v>1.1246</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8031</v>
+        <v>0.897</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3625</v>
+        <v>0.3469</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4407</v>
+        <v>0.5501</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2329</v>
+        <v>1.4285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9415</v>
+        <v>0.9981</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2914</v>
+        <v>0.4303</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4298</v>
+        <v>-0.5315</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5682</v>
+        <v>-1.527</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8313</v>
+        <v>-0.7946</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.737</v>
+        <v>-0.7323</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="9">
@@ -1111,28 +1111,28 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1189,28 +1189,28 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1303,13 +1303,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9916</v>
+        <v>-3.0035</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3452</v>
+        <v>-2.2837</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6463</v>
+        <v>-0.7197</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0159</v>
+        <v>-2.0022</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2891</v>
+        <v>-1.2793</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7268</v>
+        <v>-0.7229</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.894</v>
+        <v>-1.8509</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.296</v>
+        <v>-1.2674</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1218</v>
+        <v>-0.1513</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0069</v>
+        <v>-0.0118</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9162</v>
+        <v>-0.8902</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4651</v>
+        <v>-0.4574</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0461</v>
+        <v>-3.0815</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5872</v>
+        <v>-2.3308</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4589</v>
+        <v>-0.7507</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8404</v>
+        <v>0.8161</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0269</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8673</v>
+        <v>0.8248</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3709</v>
+        <v>-0.2236</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2672</v>
+        <v>0.4004</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2113</v>
+        <v>1.0397</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2941</v>
+        <v>-0.4091</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5053</v>
+        <v>1.4488</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8267</v>
+        <v>-0.8128</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4755</v>
+        <v>-0.4393</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3512</v>
+        <v>-0.3735</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3192</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="14">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.1871</v>
+        <v>-3.2051</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6859</v>
+        <v>-4.5513</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4988</v>
+        <v>1.3462</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2703</v>
+        <v>-1.3381</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7816</v>
+        <v>-0.8339</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4887</v>
+        <v>-0.5042</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.532</v>
+        <v>-2.4738</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.216</v>
+        <v>-1.1853</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.316</v>
+        <v>-1.2885</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2618</v>
+        <v>1.1357</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4345</v>
+        <v>0.3514</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8273</v>
+        <v>0.7843</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3166</v>
+        <v>-1.2828</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1533</v>
+        <v>-0.1301</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1634</v>
+        <v>-1.1527</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.3112</v>
+        <v>-5.3929</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.7131</v>
+        <v>-4.5176</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5981</v>
+        <v>-0.8754</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0321</v>
+        <v>-0.0439</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5278</v>
+        <v>-0.6113</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5599</v>
+        <v>0.5674</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4942</v>
+        <v>-0.4309</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1799</v>
+        <v>0.1847</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6742</v>
+        <v>-0.6156</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5263</v>
+        <v>0.387</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7078</v>
+        <v>-0.796</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2341</v>
+        <v>1.183</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0568</v>
+        <v>0.0404</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2177</v>
+        <v>-0.192</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2745</v>
+        <v>0.2324</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7269999999999994</v>
+        <v>-0.7612999999999976</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.5849</v>
+        <v>-10.4637</v>
       </c>
       <c r="F16" t="n">
-        <v>11.858</v>
+        <v>9.702400000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>4.711600000000001</v>
+        <v>4.6843</v>
       </c>
       <c r="H16" t="n">
-        <v>4.746</v>
+        <v>4.6515</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.03440000000000021</v>
+        <v>0.03280000000000027</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.8382</v>
+        <v>-1.6593</v>
       </c>
       <c r="K16" t="n">
-        <v>5.469199999999999</v>
+        <v>6.1508</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.307399999999999</v>
+        <v>-7.8102</v>
       </c>
       <c r="M16" t="n">
-        <v>7.550000000000001</v>
+        <v>6.343500000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7231000000000001</v>
+        <v>-1.4993</v>
       </c>
       <c r="O16" t="n">
-        <v>8.273199999999999</v>
+        <v>7.8428</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0006</v>
+        <v>-1.9475</v>
       </c>
       <c r="Q16" t="n">
-        <v>-17.0049</v>
+        <v>-16.5527</v>
       </c>
       <c r="R16" t="n">
-        <v>15.0043</v>
+        <v>14.6051</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.7793</v>
+        <v>-4.6977</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4992</v>
+        <v>-1.255</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.2805</v>
+        <v>-3.442699999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.341499999999999</v>
+        <v>1.1995</v>
       </c>
       <c r="W16" t="n">
-        <v>8.757400000000001</v>
+        <v>9.0032</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.415900000000001</v>
+        <v>-7.8037</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_THE FITZGERALD EL PILAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_THE FITZGERALD EL PILAR.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8635</v>
+        <v>4.059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3727</v>
+        <v>-0.1257</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4908</v>
+        <v>4.1847</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2424</v>
@@ -610,13 +610,13 @@
         <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7853</v>
+        <v>-0.0192</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6516</v>
+        <v>0.1532</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1337</v>
+        <v>-0.1724</v>
       </c>
       <c r="V2" t="n">
         <v>7.0469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4907</v>
+        <v>2.7427</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2551</v>
+        <v>2.1176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2356</v>
+        <v>0.6251</v>
       </c>
       <c r="G3" t="n">
         <v>2.6682</v>
@@ -688,13 +688,13 @@
         <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.677</v>
+        <v>-0.425</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0683</v>
+        <v>-0.2058</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6088</v>
+        <v>-0.2192</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2795</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8744</v>
+        <v>1.835</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0659</v>
+        <v>0.0338</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9403</v>
+        <v>1.8012</v>
       </c>
       <c r="G4" t="n">
         <v>0.3239</v>
@@ -766,13 +766,13 @@
         <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4758</v>
+        <v>-0.5152</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5011</v>
+        <v>-0.4015</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0253</v>
+        <v>-0.1138</v>
       </c>
       <c r="V4" t="n">
         <v>1.8316</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. LOPEZ ABAD</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2668</v>
+        <v>1.4521</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0775</v>
+        <v>0.1884</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3443</v>
+        <v>1.2637</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9409</v>
+        <v>0.897</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4111</v>
+        <v>0.3469</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4702</v>
+        <v>0.5501</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7789</v>
+        <v>1.4285</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6979</v>
+        <v>0.9981</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.4303</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1619</v>
+        <v>-0.5315</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7131999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5513</v>
+        <v>0.1198</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7789</v>
+        <v>1.3632</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7526</v>
+        <v>2.3368</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8872</v>
+        <v>-0.5286</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1172</v>
+        <v>0.0646</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0044</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4342</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4342</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. RUIPEREZ SANCHEZ</t>
+          <t>G. LOPEZ ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6384</v>
+        <v>1.3619</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7333</v>
+        <v>-0.1772</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3717</v>
+        <v>1.5391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5253</v>
+        <v>0.9409</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8364</v>
+        <v>1.4111</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3111</v>
+        <v>-0.4702</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5735</v>
+        <v>0.7789</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1232</v>
+        <v>0.6979</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6967</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0988</v>
+        <v>0.1619</v>
       </c>
       <c r="N7" t="n">
         <v>0.7131999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3856</v>
+        <v>-0.5513</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5579</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0294</v>
+        <v>-0.7921</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5344</v>
+        <v>0.0175</v>
       </c>
       <c r="U7" t="n">
-        <v>0.495</v>
+        <v>-0.8096</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5005</v>
+        <v>0.4342</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.78</v>
+        <v>0.4342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4537</v>
+        <v>0.3079</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.3079</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1246</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.897</v>
+        <v>0.3079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3469</v>
+        <v>0.3079</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5501</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4285</v>
+        <v>0.3079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9981</v>
+        <v>0.3079</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4303</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5315</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6513</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1198</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3632</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3368</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.527</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7946</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7323</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3311</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,28 +1189,28 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3079</v>
+        <v>0.1947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3079</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3079</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3079</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3079</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3079</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1225,13 +1225,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>I. RUIPEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1947</v>
+        <v>-0.2434</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1947</v>
+        <v>0.9265</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.5253</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.8364</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.3111</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.5735</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.1232</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6967</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.0988</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.3856</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1947</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1947</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.0978</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0035</v>
+        <v>-2.631</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2837</v>
+        <v>-2.0225</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7197</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0022</v>
@@ -1390,13 +1390,13 @@
         <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8902</v>
+        <v>-0.5178</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4328</v>
+        <v>-0.1717</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4574</v>
+        <v>-0.3461</v>
       </c>
       <c r="V12" t="n">
         <v>-0.89</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0815</v>
+        <v>-2.8983</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3308</v>
+        <v>-2.2311</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7507</v>
+        <v>-0.6672</v>
       </c>
       <c r="G13" t="n">
         <v>0.8161</v>
@@ -1468,13 +1468,13 @@
         <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8128</v>
+        <v>-0.6297</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4393</v>
+        <v>-0.3396</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3735</v>
+        <v>-0.2901</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1111</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.2051</v>
+        <v>-3.2977</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.5513</v>
+        <v>-4.95</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3462</v>
+        <v>1.6523</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3381</v>
@@ -1546,13 +1546,13 @@
         <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2828</v>
+        <v>-1.3754</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1301</v>
+        <v>-0.5288</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1527</v>
+        <v>-0.8466</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.3929</v>
+        <v>-5.1666</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.5176</v>
+        <v>-3.9573</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8754</v>
+        <v>-1.2093</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0439</v>
@@ -1624,13 +1624,13 @@
         <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0404</v>
+        <v>0.2667</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.192</v>
+        <v>0.3683</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2324</v>
+        <v>-0.1015</v>
       </c>
       <c r="V15" t="n">
         <v>-3.0526</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7612999999999976</v>
+        <v>-0.4520999999999997</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.4637</v>
+        <v>-10.1544</v>
       </c>
       <c r="F16" t="n">
         <v>9.702400000000001</v>
@@ -1684,7 +1684,7 @@
         <v>-7.8102</v>
       </c>
       <c r="M16" t="n">
-        <v>6.343500000000001</v>
+        <v>6.343499999999999</v>
       </c>
       <c r="N16" t="n">
         <v>-1.4993</v>
@@ -1702,19 +1702,19 @@
         <v>14.6051</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.6977</v>
+        <v>-4.3886</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.255</v>
+        <v>-0.9460000000000002</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.442699999999999</v>
+        <v>-3.4427</v>
       </c>
       <c r="V16" t="n">
         <v>1.1995</v>
       </c>
       <c r="W16" t="n">
-        <v>9.0032</v>
+        <v>9.003200000000001</v>
       </c>
       <c r="X16" t="n">
         <v>-7.8037</v>
